--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,6 +1045,823 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121596461</v>
+      </c>
+      <c r="B5" t="n">
+        <v>74707</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>308</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>495156</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6647455</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>barkfläkt björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121596460</v>
+      </c>
+      <c r="B6" t="n">
+        <v>74699</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>495156</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6647455</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>barkfläkt björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121596450</v>
+      </c>
+      <c r="B7" t="n">
+        <v>74707</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>308</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>495150</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6647372</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>barkfläkt björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121596451</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Behöver inte valideras</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>495127</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6647348</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre blåbärstallskog.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121596456</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>495050</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6647338</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121596459</v>
+      </c>
+      <c r="B10" t="n">
+        <v>95652</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>53</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>494962</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6647357</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog vid bäck.</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>barrträdslåga</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121596455</v>
+      </c>
+      <c r="B11" t="n">
+        <v>94770</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>495083</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6647328</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121596461</v>
+        <v>121596460</v>
       </c>
       <c r="B5" t="n">
-        <v>74707</v>
+        <v>74699</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,25 +1059,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596460</v>
+        <v>121596450</v>
       </c>
       <c r="B6" t="n">
-        <v>74699</v>
+        <v>74707</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,25 +1175,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495156</v>
+        <v>495150</v>
       </c>
       <c r="R6" t="n">
-        <v>6647455</v>
+        <v>6647372</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1279,14 +1279,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596450</v>
+        <v>121596451</v>
       </c>
       <c r="B7" t="n">
-        <v>74707</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1295,34 +1295,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495150</v>
+        <v>495127</v>
       </c>
       <c r="R7" t="n">
-        <v>6647372</v>
+        <v>6647348</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1368,12 +1373,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre blåbärstallskog.</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1395,55 +1400,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596451</v>
+        <v>121596455</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>94770</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495127</v>
+        <v>495083</v>
       </c>
       <c r="R8" t="n">
-        <v>6647348</v>
+        <v>6647328</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596456</v>
+        <v>121596461</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>74707</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495050</v>
+        <v>495156</v>
       </c>
       <c r="R9" t="n">
-        <v>6647338</v>
+        <v>6647455</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121596459</v>
+        <v>121596456</v>
       </c>
       <c r="B10" t="n">
-        <v>95652</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,21 +1648,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494962</v>
+        <v>495050</v>
       </c>
       <c r="R10" t="n">
-        <v>6647357</v>
+        <v>6647338</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid bäck.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>barrträdslåga</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121596455</v>
+        <v>121596459</v>
       </c>
       <c r="B11" t="n">
-        <v>94770</v>
+        <v>95652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,25 +1760,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495083</v>
+        <v>494962</v>
       </c>
       <c r="R11" t="n">
-        <v>6647328</v>
+        <v>6647357</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre barrsumpskog vid bäck.</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>barrträdslåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121596460</v>
+        <v>121596456</v>
       </c>
       <c r="B5" t="n">
-        <v>74699</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,25 +1059,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495156</v>
+        <v>495050</v>
       </c>
       <c r="R5" t="n">
-        <v>6647455</v>
+        <v>6647338</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596450</v>
+        <v>121596460</v>
       </c>
       <c r="B6" t="n">
-        <v>74707</v>
+        <v>74699</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,25 +1175,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495150</v>
+        <v>495156</v>
       </c>
       <c r="R6" t="n">
-        <v>6647372</v>
+        <v>6647455</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121596456</v>
+        <v>121596459</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>95652</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,21 +1648,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495050</v>
+        <v>494962</v>
       </c>
       <c r="R10" t="n">
-        <v>6647338</v>
+        <v>6647357</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre barrsumpskog vid bäck.</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>barrträdslåga</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121596459</v>
+        <v>121596450</v>
       </c>
       <c r="B11" t="n">
-        <v>95652</v>
+        <v>74707</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494962</v>
+        <v>495150</v>
       </c>
       <c r="R11" t="n">
-        <v>6647357</v>
+        <v>6647372</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid bäck.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>barrträdslåga</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121596456</v>
+        <v>121596455</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>94770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,25 +1059,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495050</v>
+        <v>495083</v>
       </c>
       <c r="R5" t="n">
-        <v>6647338</v>
+        <v>6647328</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1163,50 +1163,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596460</v>
+        <v>121596451</v>
       </c>
       <c r="B6" t="n">
-        <v>74699</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495156</v>
+        <v>495127</v>
       </c>
       <c r="R6" t="n">
-        <v>6647455</v>
+        <v>6647348</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1252,12 +1257,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre blåbärstallskog.</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1279,14 +1284,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596451</v>
+        <v>121596461</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>74707</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1295,39 +1300,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495127</v>
+        <v>495156</v>
       </c>
       <c r="R7" t="n">
-        <v>6647348</v>
+        <v>6647455</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596455</v>
+        <v>121596450</v>
       </c>
       <c r="B8" t="n">
-        <v>94770</v>
+        <v>74707</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,25 +1412,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495083</v>
+        <v>495150</v>
       </c>
       <c r="R8" t="n">
-        <v>6647328</v>
+        <v>6647372</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596461</v>
+        <v>121596459</v>
       </c>
       <c r="B9" t="n">
-        <v>74707</v>
+        <v>95652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495156</v>
+        <v>494962</v>
       </c>
       <c r="R9" t="n">
-        <v>6647455</v>
+        <v>6647357</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre barrsumpskog vid bäck.</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>barrträdslåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121596459</v>
+        <v>121596456</v>
       </c>
       <c r="B10" t="n">
-        <v>95652</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,21 +1648,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494962</v>
+        <v>495050</v>
       </c>
       <c r="R10" t="n">
-        <v>6647357</v>
+        <v>6647338</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid bäck.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>barrträdslåga</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121596450</v>
+        <v>121596460</v>
       </c>
       <c r="B11" t="n">
-        <v>74707</v>
+        <v>74699</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,25 +1760,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495150</v>
+        <v>495156</v>
       </c>
       <c r="R11" t="n">
-        <v>6647372</v>
+        <v>6647455</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -1047,14 +1047,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121596450</v>
+        <v>121596451</v>
       </c>
       <c r="B5" t="n">
-        <v>74714</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1063,34 +1063,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495150</v>
+        <v>495127</v>
       </c>
       <c r="R5" t="n">
-        <v>6647372</v>
+        <v>6647348</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1136,12 +1141,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre blåbärstallskog.</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1163,14 +1168,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596451</v>
+        <v>121596461</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>74714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1179,39 +1184,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495127</v>
+        <v>495156</v>
       </c>
       <c r="R6" t="n">
-        <v>6647348</v>
+        <v>6647455</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596461</v>
+        <v>121596455</v>
       </c>
       <c r="B8" t="n">
-        <v>74714</v>
+        <v>94778</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,25 +1412,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495156</v>
+        <v>495083</v>
       </c>
       <c r="R8" t="n">
-        <v>6647455</v>
+        <v>6647328</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596455</v>
+        <v>121596460</v>
       </c>
       <c r="B9" t="n">
-        <v>94778</v>
+        <v>74706</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>6439</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495083</v>
+        <v>495156</v>
       </c>
       <c r="R9" t="n">
-        <v>6647328</v>
+        <v>6647455</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121596456</v>
+        <v>121596450</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>74714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,21 +1648,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495050</v>
+        <v>495150</v>
       </c>
       <c r="R10" t="n">
-        <v>6647338</v>
+        <v>6647372</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121596460</v>
+        <v>121596456</v>
       </c>
       <c r="B11" t="n">
-        <v>74706</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,25 +1760,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495156</v>
+        <v>495050</v>
       </c>
       <c r="R11" t="n">
-        <v>6647455</v>
+        <v>6647338</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -1047,14 +1047,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121596451</v>
+        <v>121596461</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>74714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1063,39 +1063,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495127</v>
+        <v>495156</v>
       </c>
       <c r="R5" t="n">
-        <v>6647348</v>
+        <v>6647455</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1141,12 +1136,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,14 +1163,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596461</v>
+        <v>121596451</v>
       </c>
       <c r="B6" t="n">
-        <v>74714</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1184,34 +1179,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495156</v>
+        <v>495127</v>
       </c>
       <c r="R6" t="n">
-        <v>6647455</v>
+        <v>6647348</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre blåbärstallskog.</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121596461</v>
+        <v>121596460</v>
       </c>
       <c r="B5" t="n">
-        <v>74714</v>
+        <v>74706</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,25 +1059,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1163,14 +1163,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596451</v>
+        <v>121596456</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1179,39 +1179,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495127</v>
+        <v>495050</v>
       </c>
       <c r="R6" t="n">
-        <v>6647348</v>
+        <v>6647338</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1257,12 +1252,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1284,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596459</v>
+        <v>121596461</v>
       </c>
       <c r="B7" t="n">
-        <v>95660</v>
+        <v>74714</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,21 +1295,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1324,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494962</v>
+        <v>495156</v>
       </c>
       <c r="R7" t="n">
-        <v>6647357</v>
+        <v>6647455</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1373,12 +1368,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid bäck.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>barrträdslåga</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1400,50 +1395,55 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596455</v>
+        <v>121596451</v>
       </c>
       <c r="B8" t="n">
-        <v>94778</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495083</v>
+        <v>495127</v>
       </c>
       <c r="R8" t="n">
-        <v>6647328</v>
+        <v>6647348</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre blåbärstallskog.</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596460</v>
+        <v>121596455</v>
       </c>
       <c r="B9" t="n">
-        <v>74706</v>
+        <v>94778</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6439</v>
+        <v>2170</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495156</v>
+        <v>495083</v>
       </c>
       <c r="R9" t="n">
-        <v>6647455</v>
+        <v>6647328</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121596450</v>
+        <v>121596459</v>
       </c>
       <c r="B10" t="n">
-        <v>74714</v>
+        <v>95660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,21 +1648,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495150</v>
+        <v>494962</v>
       </c>
       <c r="R10" t="n">
-        <v>6647372</v>
+        <v>6647357</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre barrsumpskog vid bäck.</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>barrträdslåga</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121596456</v>
+        <v>121596450</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>74714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495050</v>
+        <v>495150</v>
       </c>
       <c r="R11" t="n">
-        <v>6647338</v>
+        <v>6647372</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -1395,55 +1395,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596451</v>
+        <v>121596455</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>94778</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495127</v>
+        <v>495083</v>
       </c>
       <c r="R8" t="n">
-        <v>6647348</v>
+        <v>6647328</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1489,12 +1484,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1516,50 +1511,55 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596455</v>
+        <v>121596451</v>
       </c>
       <c r="B9" t="n">
-        <v>94778</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495083</v>
+        <v>495127</v>
       </c>
       <c r="R9" t="n">
-        <v>6647328</v>
+        <v>6647348</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre blåbärstallskog.</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -1279,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596461</v>
+        <v>121596455</v>
       </c>
       <c r="B7" t="n">
-        <v>74714</v>
+        <v>94778</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,25 +1291,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495156</v>
+        <v>495083</v>
       </c>
       <c r="R7" t="n">
-        <v>6647455</v>
+        <v>6647328</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1395,50 +1395,55 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596455</v>
+        <v>121596451</v>
       </c>
       <c r="B8" t="n">
-        <v>94778</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495083</v>
+        <v>495127</v>
       </c>
       <c r="R8" t="n">
-        <v>6647328</v>
+        <v>6647348</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1484,12 +1489,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre blåbärstallskog.</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1511,14 +1516,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596451</v>
+        <v>121596450</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>74714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1527,39 +1532,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495127</v>
+        <v>495150</v>
       </c>
       <c r="R9" t="n">
-        <v>6647348</v>
+        <v>6647372</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121596459</v>
+        <v>121596461</v>
       </c>
       <c r="B10" t="n">
-        <v>95660</v>
+        <v>74714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,21 +1648,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494962</v>
+        <v>495156</v>
       </c>
       <c r="R10" t="n">
-        <v>6647357</v>
+        <v>6647455</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid bäck.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>barrträdslåga</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121596450</v>
+        <v>121596459</v>
       </c>
       <c r="B11" t="n">
-        <v>74714</v>
+        <v>95660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495150</v>
+        <v>494962</v>
       </c>
       <c r="R11" t="n">
-        <v>6647372</v>
+        <v>6647357</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre barrsumpskog vid bäck.</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>barrträdslåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -1047,50 +1047,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121596460</v>
+        <v>121596451</v>
       </c>
       <c r="B5" t="n">
-        <v>74706</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495156</v>
+        <v>495127</v>
       </c>
       <c r="R5" t="n">
-        <v>6647455</v>
+        <v>6647348</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1136,12 +1141,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre blåbärstallskog.</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1163,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596456</v>
+        <v>121596455</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>94778</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,25 +1180,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495050</v>
+        <v>495083</v>
       </c>
       <c r="R6" t="n">
-        <v>6647338</v>
+        <v>6647328</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1257,7 +1262,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1279,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596455</v>
+        <v>121596456</v>
       </c>
       <c r="B7" t="n">
-        <v>94778</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,25 +1296,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1319,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495083</v>
+        <v>495050</v>
       </c>
       <c r="R7" t="n">
-        <v>6647328</v>
+        <v>6647338</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1373,7 +1378,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1395,14 +1400,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596451</v>
+        <v>121596461</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>74714</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1411,39 +1416,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495127</v>
+        <v>495156</v>
       </c>
       <c r="R8" t="n">
-        <v>6647348</v>
+        <v>6647455</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121596461</v>
+        <v>121596459</v>
       </c>
       <c r="B10" t="n">
-        <v>74714</v>
+        <v>95660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,21 +1648,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495156</v>
+        <v>494962</v>
       </c>
       <c r="R10" t="n">
-        <v>6647455</v>
+        <v>6647357</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre barrsumpskog vid bäck.</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>barrträdslåga</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121596459</v>
+        <v>121596460</v>
       </c>
       <c r="B11" t="n">
-        <v>95660</v>
+        <v>74706</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,25 +1760,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494962</v>
+        <v>495156</v>
       </c>
       <c r="R11" t="n">
-        <v>6647357</v>
+        <v>6647455</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid bäck.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>barrträdslåga</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -1047,14 +1047,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121596451</v>
+        <v>121596456</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1063,39 +1063,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495127</v>
+        <v>495050</v>
       </c>
       <c r="R5" t="n">
-        <v>6647348</v>
+        <v>6647338</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1141,12 +1136,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1284,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596456</v>
+        <v>121596450</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>74714</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,21 +1295,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1324,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495050</v>
+        <v>495150</v>
       </c>
       <c r="R7" t="n">
-        <v>6647338</v>
+        <v>6647372</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1378,7 +1373,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1400,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596461</v>
+        <v>121596460</v>
       </c>
       <c r="B8" t="n">
-        <v>74714</v>
+        <v>74706</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,25 +1407,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1516,14 +1511,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596450</v>
+        <v>121596451</v>
       </c>
       <c r="B9" t="n">
-        <v>74714</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1532,34 +1527,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495150</v>
+        <v>495127</v>
       </c>
       <c r="R9" t="n">
-        <v>6647372</v>
+        <v>6647348</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre blåbärstallskog.</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121596459</v>
+        <v>121596461</v>
       </c>
       <c r="B10" t="n">
-        <v>95660</v>
+        <v>74714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,21 +1648,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494962</v>
+        <v>495156</v>
       </c>
       <c r="R10" t="n">
-        <v>6647357</v>
+        <v>6647455</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid bäck.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>barrträdslåga</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121596460</v>
+        <v>121596459</v>
       </c>
       <c r="B11" t="n">
-        <v>74706</v>
+        <v>95660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,25 +1760,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495156</v>
+        <v>494962</v>
       </c>
       <c r="R11" t="n">
-        <v>6647455</v>
+        <v>6647357</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre barrsumpskog vid bäck.</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>barrträdslåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121596456</v>
+        <v>121596461</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>74714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,21 +1063,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495050</v>
+        <v>495156</v>
       </c>
       <c r="R5" t="n">
-        <v>6647338</v>
+        <v>6647455</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1163,50 +1163,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596455</v>
+        <v>121596451</v>
       </c>
       <c r="B6" t="n">
-        <v>94778</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495083</v>
+        <v>495127</v>
       </c>
       <c r="R6" t="n">
-        <v>6647328</v>
+        <v>6647348</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1252,12 +1257,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre blåbärstallskog.</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1279,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596450</v>
+        <v>121596459</v>
       </c>
       <c r="B7" t="n">
-        <v>74714</v>
+        <v>95660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,21 +1300,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1319,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495150</v>
+        <v>494962</v>
       </c>
       <c r="R7" t="n">
-        <v>6647372</v>
+        <v>6647357</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1368,12 +1373,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog.</t>
+          <t>Äldre barrsumpskog vid bäck.</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>barrträdslåga</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1395,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596460</v>
+        <v>121596455</v>
       </c>
       <c r="B8" t="n">
-        <v>74706</v>
+        <v>94778</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1416,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6439</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495156</v>
+        <v>495083</v>
       </c>
       <c r="R8" t="n">
-        <v>6647455</v>
+        <v>6647328</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1489,7 +1494,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1511,55 +1516,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596451</v>
+        <v>121596460</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>74706</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495127</v>
+        <v>495156</v>
       </c>
       <c r="R9" t="n">
-        <v>6647348</v>
+        <v>6647455</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121596461</v>
+        <v>121596456</v>
       </c>
       <c r="B10" t="n">
-        <v>74714</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,21 +1648,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495156</v>
+        <v>495050</v>
       </c>
       <c r="R10" t="n">
-        <v>6647455</v>
+        <v>6647338</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121596459</v>
+        <v>121596450</v>
       </c>
       <c r="B11" t="n">
-        <v>95660</v>
+        <v>74714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494962</v>
+        <v>495150</v>
       </c>
       <c r="R11" t="n">
-        <v>6647357</v>
+        <v>6647372</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid bäck.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>barrträdslåga</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90813271</v>
+        <v>121596453</v>
       </c>
       <c r="B2" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495018.8566353925</v>
+        <v>495091</v>
       </c>
       <c r="R2" t="n">
-        <v>6647377.158519654</v>
+        <v>6647304</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,16 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -796,58 +786,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96016623</v>
+        <v>121596459</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494991.7576296239</v>
+        <v>494962</v>
       </c>
       <c r="R3" t="n">
-        <v>6647368.181407188</v>
+        <v>6647357</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,81 +868,82 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AN3" t="n">
-        <v>1</v>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog vid bäck.</t>
+        </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>barrträdslåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Andersson, Mattias Sterner</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82384286</v>
+        <v>125474315</v>
       </c>
       <c r="B4" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Vikafall, Vikafall, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495056.9144852902</v>
+        <v>495053</v>
       </c>
       <c r="R4" t="n">
-        <v>6647329.033901451</v>
+        <v>6647321</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,22 +967,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-11-21</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-11-21</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,39 +994,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Barklös tallåga.</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Niklas Trogen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121596450</v>
+        <v>121596449</v>
       </c>
       <c r="B5" t="n">
-        <v>74727</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1049,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495150</v>
+        <v>495174</v>
       </c>
       <c r="R5" t="n">
         <v>6647372</v>
@@ -1163,15 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596461</v>
+        <v>121596450</v>
       </c>
       <c r="B6" t="n">
-        <v>74727</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495156</v>
+        <v>495150</v>
       </c>
       <c r="R6" t="n">
-        <v>6647455</v>
+        <v>6647372</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1279,37 +1236,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121596455</v>
+        <v>121596461</v>
       </c>
       <c r="B7" t="n">
-        <v>94796</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1319,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495083</v>
+        <v>495156</v>
       </c>
       <c r="R7" t="n">
-        <v>6647328</v>
+        <v>6647455</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1373,7 +1325,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1395,37 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121596456</v>
+        <v>121596455</v>
       </c>
       <c r="B8" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495050</v>
+        <v>495083</v>
       </c>
       <c r="R8" t="n">
-        <v>6647338</v>
+        <v>6647328</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1489,7 +1436,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1511,55 +1458,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121596451</v>
+        <v>121596454</v>
       </c>
       <c r="B9" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495127</v>
+        <v>495091</v>
       </c>
       <c r="R9" t="n">
-        <v>6647348</v>
+        <v>6647310</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1605,12 +1542,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre blåbärstallskog.</t>
+          <t>Äldre barrsumpskog.</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1632,53 +1569,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121596459</v>
+        <v>82384287</v>
       </c>
       <c r="B10" t="n">
-        <v>95678</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hörksälven, Vstm</t>
+          <t>Hörkälven, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494962</v>
+        <v>495157</v>
       </c>
       <c r="R10" t="n">
-        <v>6647357</v>
+        <v>6647462</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1702,12 +1634,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2019-11-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2019-11-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,26 +1650,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre barrsumpskog vid bäck.</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>barrträdslåga</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Jesper Hansson, Siverrt Juneholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1748,37 +1670,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121596460</v>
+        <v>121596456</v>
       </c>
       <c r="B11" t="n">
-        <v>74719</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1788,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495156</v>
+        <v>495050</v>
       </c>
       <c r="R11" t="n">
-        <v>6647455</v>
+        <v>6647338</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1842,7 +1759,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1861,6 +1778,883 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121596462</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>495160</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6647435</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121596460</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>495156</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6647455</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>barkfläkt björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>90813095</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>495134</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6647473</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121596451</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>495127</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6647348</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Äldre blåbärstallskog.</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>82384284</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>495026</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6647438</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2019-11-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2019-11-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Gammal senvuxen gran. 1 dm dbh.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>82384286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>495057</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6647329</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-11-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-11-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Barklös tallåga.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>90813271</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>495019</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6647377</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>96016623</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>494992</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6647368</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Michael Andersson, Mattias Sterner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65215-2021 artfynd.xlsx
+++ b/artfynd/A 65215-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596453</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596459</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125474315</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596449</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596450</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596461</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1455,6 +1490,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596455</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596454</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82384287</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596456</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596462</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2000,6 +2060,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596460</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2101,6 +2166,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90813095</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2217,6 +2287,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596451</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2328,6 +2403,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82384284</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2439,6 +2519,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82384286</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2545,6 +2630,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90813271</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2655,8 +2745,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96016623</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>